--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,67 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1514,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1536,23 +1528,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,21 +1586,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1652,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1671,8 +1679,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1680,63 +1696,47 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,21 +1754,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1812,19 +1820,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1868,19 +1876,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1924,19 +1932,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1980,19 +1988,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2026,29 +2034,21 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,64 +2111,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2176,23 +2168,31 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,21 +2226,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2284,24 +2292,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2311,72 +2319,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,21 +2394,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2452,19 +2460,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2482,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2516,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2564,19 +2572,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2628,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2642,53 +2650,45 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>National requirement types[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2698,34 +2698,34 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>community-consultation</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2736,12 +2736,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2751,16 +2751,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>community-consultation</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>What community consultation activities have taken place as part of the application</t>
@@ -2768,12 +2760,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>have-consulted</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2784,36 +2776,44 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2824,31 +2824,23 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2856,12 +2848,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2872,17 +2864,17 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2888,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,7 +2904,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2927,21 +2919,29 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -2962,21 +2962,13 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2984,12 +2976,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -3000,12 +2992,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3024,12 +3016,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3040,12 +3032,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3055,21 +3047,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Demolition</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>demolition</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>is-proposing-demolition</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Is propsing demolition</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3080,12 +3080,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Does the proposal include partial or total demolition of a listed building?</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3095,16 +3095,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Demolition</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>demolition</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Details of any demolition that needs to take place as part of the development proposal.</t>
@@ -3112,12 +3104,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>is-proposing-demolition</t>
+          <t>is-total-demolition</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Is propsing demolition</t>
+          <t>Is total demolition</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3128,7 +3120,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include partial or total demolition of a listed building?</t>
+          <t>Indicating whether the proposal involves total demolition of a listed building</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3138,7 +3130,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3144,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>is-total-demolition</t>
+          <t>is-demolishing-building-in-curtilage</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Is total demolition</t>
+          <t>Demolition building in curtilage</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3168,7 +3160,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Indicating whether the proposal involves total demolition of a listed building</t>
+          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3192,12 +3184,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>is-demolishing-building-in-curtilage</t>
+          <t>is-partial-demolition</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Demolition building in curtilage</t>
+          <t>Demolition part</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3208,7 +3200,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
+          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3232,12 +3224,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>is-partial-demolition</t>
+          <t>listed-building-volume</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Demolition part</t>
+          <t>Listed building volume</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3248,12 +3240,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
+          <t>Volume of listed building in cubic metres</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3272,12 +3264,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>listed-building-volume</t>
+          <t>demolition-volume</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Listed building volume</t>
+          <t>Demolition volume</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3288,7 +3280,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Volume of listed building in cubic metres</t>
+          <t>Volume of part to be demolished in cubic metres</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3312,12 +3304,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>demolition-volume</t>
+          <t>part-built-date</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Demolition volume</t>
+          <t>Part built date</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3328,12 +3320,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Volume of part to be demolished in cubic metres</t>
+          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3352,12 +3344,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>part-built-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Part built date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3368,17 +3360,17 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
+          <t>Description of the building or part you are proposing to demolish</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3384,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3408,7 +3400,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Description of the building or part you are proposing to demolish</t>
+          <t>Reason for demolition</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3423,21 +3415,29 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="2" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Immunity from listing</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>immunity-from-listing</t>
+        </is>
+      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>cert-of-immunity-sought</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Certificate of immunity sought</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Reason for demolition</t>
+          <t>Has a certificate of immunity been sought</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3463,16 +3463,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Immunity from listing</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>immunity-from-listing</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
@@ -3480,12 +3472,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>cert-of-immunity-sought</t>
+          <t>application-result</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Certificate of immunity sought</t>
+          <t>Application result</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3496,36 +3488,44 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Has a certificate of immunity been sought</t>
+          <t>Provide the result of the application for a certificate of immunity</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Listed building alterations</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>lb-alter</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
+          <t>Details of any changes being made to a listed building as part of development works</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>application-result</t>
+          <t>proposal-alter-lb</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Application result</t>
+          <t>Proposal alter listed building</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3536,31 +3536,23 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Provide the result of the application for a certificate of immunity</t>
+          <t>True or False if proposal includes alterations to a listed building</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Listed building alterations</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>lb-alter</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Details of any changes being made to a listed building as part of development works</t>
@@ -3568,12 +3560,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>proposal-alter-lb</t>
+          <t>proposal-alter-lb-types</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Proposal alter listed building</t>
+          <t>Proposal alteration types[]</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3584,17 +3576,17 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>True or False if proposal includes alterations to a listed building</t>
+          <t>Select from a list of listed building alteration types, select all that apply</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3608,76 +3600,84 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>proposal-alter-lb-types</t>
+          <t>document-reference</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Proposal alteration types[]</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Select from a list of listed building alteration types, select all that apply</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>lb-grade</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>document-reference</t>
+          <t>listed-building-grade</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3687,16 +3687,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>lb-grade</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>The grade of any listed building affected by the proposed development.</t>
@@ -3704,12 +3696,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>listed-building-grade</t>
+          <t>listed-building</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3720,17 +3712,17 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3744,12 +3736,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>listed-building</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3760,12 +3752,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3775,32 +3767,48 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>building-element-type</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Building element type</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3810,21 +3818,13 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>building-element-type</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Building element type</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3856,17 +3856,17 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3890,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>materials-not-applicable</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Materials not applicable</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3952,12 +3952,12 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Indicates this building element is not relevant to the application</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>materials-not-applicable</t>
+          <t>materials-not-known</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -4000,7 +4000,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4024,31 +4024,23 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>materials-not-known</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Materials not known</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4058,7 +4050,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4072,28 +4064,36 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4103,45 +4103,45 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4151,16 +4151,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -4168,33 +4160,49 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>lbc-owners</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4228,19 +4236,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4250,7 +4258,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4284,19 +4292,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4340,19 +4348,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4396,19 +4404,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4418,7 +4426,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4442,34 +4450,26 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>notice-date</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Notice date</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4488,36 +4488,28 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>lbc-owners</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>notice-date</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Notice date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4536,23 +4528,31 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>publication-date</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Publication date</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4600,12 +4600,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4624,41 +4624,33 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4672,12 +4664,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>applicant-signature</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
+          <t>Applicant signature</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4688,12 +4680,12 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Digital signature of the applicant</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -4712,12 +4704,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>agent-signature</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
+          <t>Agent signature</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4728,7 +4720,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Digital signature of the agent (if applicable)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4752,12 +4744,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4768,7 +4760,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -4783,21 +4775,29 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="2" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4808,31 +4808,23 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4840,12 +4832,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4856,17 +4848,17 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4880,12 +4872,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4896,7 +4888,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -4920,12 +4912,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4936,7 +4928,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -4960,12 +4952,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -4976,7 +4968,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -4991,21 +4983,29 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>proposal-description</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5026,21 +5026,13 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -5048,12 +5040,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5064,12 +5056,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5088,12 +5080,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5104,17 +5096,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5120,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -5144,17 +5136,17 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5160,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -5184,36 +5176,44 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="2" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Has related applications</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5224,60 +5224,60 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Details of any other development proposals made for the site</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>related-applications</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Details of any other development proposals made for the site</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>has-related-applications</t>
-        </is>
-      </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>Related applications[]</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5320,7 +5320,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5368,7 +5368,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -5378,36 +5378,44 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5416,12 +5424,12 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -5431,16 +5439,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5472,12 +5472,12 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5520,7 +5520,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5568,12 +5568,12 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5616,7 +5616,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5664,7 +5664,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5712,7 +5712,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
@@ -5760,12 +5760,12 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5808,7 +5808,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5823,64 +5823,56 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="n"/>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5888,12 +5880,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -5904,12 +5896,12 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -5928,12 +5920,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -5944,17 +5936,17 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5968,23 +5960,31 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -6018,12 +6018,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -6032,7 +6032,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
@@ -6080,7 +6080,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -6089,54 +6089,6 @@
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n"/>
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M117" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6144,46 +6096,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A103:A111"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B68:B74"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B103:B111"/>
-    <mergeCell ref="B75:B88"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="B94:B98"/>
-    <mergeCell ref="A68:A74"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B51:B59"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A94:A98"/>
-    <mergeCell ref="A112:A117"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A75:A88"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B112:B117"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A51:A59"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A89:A93"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B88:B92"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="A50:A58"/>
+    <mergeCell ref="B74:B87"/>
+    <mergeCell ref="A111:A116"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B111:B116"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="A93:A97"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A88:A92"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A102:A110"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="B50:B58"/>
+    <mergeCell ref="B93:B97"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A74:A87"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B102:B110"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B67:B73"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -5373,7 +5373,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -3037,7 +3037,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>proposal-description</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -435,8 +435,8 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -3784,36 +3784,28 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3842,12 +3834,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3856,17 +3848,17 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3882,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3904,7 +3896,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3938,12 +3930,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>materials-not-applicable</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Materials not applicable</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3952,12 +3944,12 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Indicates this building element is not relevant to the application</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,67 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1528,31 +1536,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1644,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1679,16 +1671,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1696,47 +1680,63 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,29 +1754,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,19 +1812,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1868,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1932,19 +1924,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1988,19 +1980,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2026,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,56 +2111,64 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2168,31 +2176,23 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,29 +2226,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2284,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2319,64 +2311,72 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,29 +2394,21 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2460,19 +2452,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2482,7 +2474,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2516,19 +2508,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2572,19 +2564,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2628,19 +2620,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2650,45 +2642,53 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2698,34 +2698,34 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Community consultation</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>community-consultation</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>What community consultation activities have taken place as part of the application</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>have-consulted</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Have consulted</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2736,12 +2736,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Whether community consultation has been carried out</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2751,8 +2751,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Community consultation</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>community-consultation</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>What community consultation activities have taken place as part of the application</t>
@@ -2760,12 +2768,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2776,44 +2784,36 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2824,23 +2824,31 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2848,12 +2856,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,17 +2872,17 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2896,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2904,7 +2912,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2919,29 +2927,21 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -2962,13 +2962,21 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2976,12 +2984,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,12 +3000,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3016,12 +3024,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3032,12 +3040,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3047,29 +3055,21 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Demolition</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>demolition</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>is-proposing-demolition</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Is propsing demolition</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3080,12 +3080,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include partial or total demolition of a listed building?</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3095,8 +3095,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Demolition</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>demolition</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Details of any demolition that needs to take place as part of the development proposal.</t>
@@ -3104,12 +3112,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>is-total-demolition</t>
+          <t>is-proposing-demolition</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Is total demolition</t>
+          <t>Is propsing demolition</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3120,7 +3128,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Indicating whether the proposal involves total demolition of a listed building</t>
+          <t>Does the proposal include partial or total demolition of a listed building?</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3130,7 +3138,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3152,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>is-demolishing-building-in-curtilage</t>
+          <t>is-total-demolition</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Demolition building in curtilage</t>
+          <t>Is total demolition</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3160,7 +3168,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
+          <t>Indicating whether the proposal involves total demolition of a listed building</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3184,12 +3192,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>is-partial-demolition</t>
+          <t>is-demolishing-building-in-curtilage</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Demolition part</t>
+          <t>Demolition building in curtilage</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3200,7 +3208,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
+          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3224,12 +3232,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>listed-building-volume</t>
+          <t>is-partial-demolition</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Listed building volume</t>
+          <t>Demolition part</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3240,12 +3248,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Volume of listed building in cubic metres</t>
+          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -3264,12 +3272,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>demolition-volume</t>
+          <t>listed-building-volume</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Demolition volume</t>
+          <t>Listed building volume</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3280,12 +3288,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Volume of part to be demolished in cubic metres</t>
+          <t>Volume of listed building in cubic metres</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3304,12 +3312,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>part-built-date</t>
+          <t>demolition-volume</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Part built date</t>
+          <t>Demolition volume</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3320,12 +3328,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
+          <t>Volume of part to be demolished in cubic metres</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3344,12 +3352,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>part-built-date</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Part built date</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3360,17 +3368,17 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Description of the building or part you are proposing to demolish</t>
+          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3392,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3400,7 +3408,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Reason for demolition</t>
+          <t>Description of the building or part you are proposing to demolish</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3415,29 +3423,21 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Immunity from listing</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>immunity-from-listing</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>cert-of-immunity-sought</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Certificate of immunity sought</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Has a certificate of immunity been sought</t>
+          <t>Reason for demolition</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -3463,8 +3463,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Immunity from listing</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>immunity-from-listing</t>
+        </is>
+      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
@@ -3472,12 +3480,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>application-result</t>
+          <t>cert-of-immunity-sought</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Application result</t>
+          <t>Certificate of immunity sought</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3488,44 +3496,36 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Provide the result of the application for a certificate of immunity</t>
+          <t>Has a certificate of immunity been sought</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Listed building alterations</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>lb-alter</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>proposal-alter-lb</t>
+          <t>application-result</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Proposal alter listed building</t>
+          <t>Application result</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3536,23 +3536,31 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>True or False if proposal includes alterations to a listed building</t>
+          <t>Provide the result of the application for a certificate of immunity</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Listed building alterations</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>lb-alter</t>
+        </is>
+      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Details of any changes being made to a listed building as part of development works</t>
@@ -3560,12 +3568,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>proposal-alter-lb-types</t>
+          <t>proposal-alter-lb</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Proposal alteration types[]</t>
+          <t>Proposal alter listed building</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3576,17 +3584,17 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Select from a list of listed building alteration types, select all that apply</t>
+          <t>True or False if proposal includes alterations to a listed building</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3600,84 +3608,76 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>document-reference</t>
+          <t>proposal-alter-lb-types</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal alteration types[]</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Select from a list of listed building alteration types, select all that apply</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>lb-grade</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>Details of any changes being made to a listed building as part of development works</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>listed-building-grade</t>
+          <t>document-reference</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3687,8 +3687,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>lb-grade</t>
+        </is>
+      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>The grade of any listed building affected by the proposed development.</t>
@@ -3696,12 +3704,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>listed-building</t>
+          <t>listed-building-grade</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3712,17 +3720,17 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3744,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>listed-building</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3752,12 +3760,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3767,29 +3775,21 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>proposal-material-details</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3800,23 +3800,31 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -3824,36 +3832,28 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>existing-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Existing materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3896,17 +3896,17 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3930,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3944,7 +3944,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>proposed-materials</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Proposed materials</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3992,12 +3992,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4016,23 +4016,31 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>materials-not-known</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Materials not known</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4042,7 +4050,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4056,36 +4064,28 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Providing additional material information</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4095,45 +4095,45 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+          <t>Supporting documents[]</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4143,8 +4143,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -4152,49 +4160,33 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>lbc-owners</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4228,19 +4220,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4250,7 +4242,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4284,19 +4276,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4340,19 +4332,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4396,19 +4388,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4418,7 +4410,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4442,26 +4434,34 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>notice-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Notice date</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4480,28 +4480,36 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>lbc-owners</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>notice-served-date</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Notice served date</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -4520,41 +4528,33 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>newspaper-name</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Newspaper name</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4568,41 +4568,33 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Steps taken</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4616,33 +4608,41 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4656,33 +4656,41 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>applicant-signature</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Applicant signature</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the applicant</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4704,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>agent-signature</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Agent signature</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4712,7 +4720,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Digital signature of the agent (if applicable)</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4722,7 +4730,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4744,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4752,44 +4760,36 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4800,12 +4800,12 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4815,8 +4815,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4824,12 +4832,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4840,17 +4848,17 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4872,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4880,7 +4888,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -4904,12 +4912,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4920,12 +4928,12 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -4944,12 +4952,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -4960,12 +4968,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -4975,29 +4983,21 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5008,7 +5008,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5018,13 +5018,21 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="2" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -5032,12 +5040,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5048,12 +5056,12 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5072,12 +5080,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5088,17 +5096,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5112,12 +5120,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -5128,17 +5136,17 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5160,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal completed</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -5168,44 +5176,36 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>related-applications</t>
-        </is>
-      </c>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>has-related-applications</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal completion date</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5216,23 +5216,31 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n"/>
-      <c r="B99" s="2" t="n"/>
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Details of any other development proposals made for the site</t>
@@ -5240,36 +5248,28 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>decision-date</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Decision date</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5360,54 +5360,46 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5416,12 +5408,12 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -5431,8 +5423,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
-      <c r="B103" s="2" t="n"/>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5464,12 +5464,12 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5512,7 +5512,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5560,12 +5560,12 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5608,12 +5608,12 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5656,12 +5656,12 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
@@ -5704,12 +5704,12 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
@@ -5752,12 +5752,12 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5800,7 +5800,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5815,56 +5815,64 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n"/>
-      <c r="B112" s="2" t="n"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5872,12 +5880,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -5888,12 +5896,12 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -5912,12 +5920,12 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -5928,17 +5936,17 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5952,31 +5960,23 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6010,12 +6010,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -6024,7 +6024,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
@@ -6072,15 +6072,63 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="M117" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6088,46 +6136,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="B88:B92"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="A50:A58"/>
-    <mergeCell ref="B74:B87"/>
-    <mergeCell ref="A111:A116"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B41"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B111:B116"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A93:A97"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A88:A92"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A102:A110"/>
-    <mergeCell ref="A41"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="B50:B58"/>
-    <mergeCell ref="B93:B97"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A74:A87"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B102:B110"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B67:B73"/>
-    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A103:A111"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B68:B74"/>
+    <mergeCell ref="A99:A102"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B103:B111"/>
+    <mergeCell ref="B75:B88"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B89:B93"/>
+    <mergeCell ref="B94:B98"/>
+    <mergeCell ref="A68:A74"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B42"/>
+    <mergeCell ref="A94:A98"/>
+    <mergeCell ref="A112:A117"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A75:A88"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B112:B117"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A51:A59"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A42"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A89:A93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/listed-building-consent-lbc-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,21 +2098,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,12 +2162,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2144,12 +2176,12 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,56 +2191,64 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2216,31 +2256,23 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,29 +2306,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2364,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2367,64 +2391,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2442,29 +2474,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2588,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2644,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2676,144 +2700,192 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Checklist</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>checklist</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>national-req-types</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>List of the document types required for the given application type</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>community-consultation</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>have-consulted</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Have consulted</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Whether community consultation has been carried out</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2824,7 +2896,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2834,34 +2906,34 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>community-consultation</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2872,7 +2944,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2891,17 +2963,17 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,7 +2984,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2927,8 +2999,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2936,12 +3016,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,34 +3032,26 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3000,7 +3072,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3010,7 +3082,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3019,17 +3091,17 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3040,23 +3112,31 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3064,12 +3144,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3080,12 +3160,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3095,29 +3175,21 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Demolition</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>demolition</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>is-proposing-demolition</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Is propsing demolition</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3128,7 +3200,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Does the proposal include partial or total demolition of a listed building?</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3147,17 +3219,17 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>is-total-demolition</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Is total demolition</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3168,23 +3240,31 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Indicating whether the proposal involves total demolition of a listed building</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Demolition</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>demolition</t>
+        </is>
+      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Details of any demolition that needs to take place as part of the development proposal.</t>
@@ -3192,12 +3272,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>is-demolishing-building-in-curtilage</t>
+          <t>is-proposing-demolition</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Demolition building in curtilage</t>
+          <t>Is propsing demolition</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3208,7 +3288,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
+          <t>Does the proposal include partial or total demolition of a listed building?</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3218,7 +3298,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3312,12 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>is-partial-demolition</t>
+          <t>is-total-demolition</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Demolition part</t>
+          <t>Is total demolition</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3248,7 +3328,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
+          <t>Indicating whether the proposal involves total demolition of a listed building</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3272,12 +3352,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>listed-building-volume</t>
+          <t>is-demolishing-building-in-curtilage</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Listed building volume</t>
+          <t>Demolition building in curtilage</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3288,12 +3368,12 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Volume of listed building in cubic metres</t>
+          <t>True or False indicating whether the proposal involves demolition of a building in the curtilage of a listed building</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3312,12 +3392,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>demolition-volume</t>
+          <t>is-partial-demolition</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Demolition volume</t>
+          <t>Demolition part</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3328,12 +3408,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Volume of part to be demolished in cubic metres</t>
+          <t>True or False indicating whether the proposal involves partial demolition of a listed building</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -3352,12 +3432,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>part-built-date</t>
+          <t>listed-building-volume</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Part built date</t>
+          <t>Listed building volume</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3368,12 +3448,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
+          <t>Volume of listed building in cubic metres</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -3392,12 +3472,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>demolition-volume</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Demolition volume</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3408,17 +3488,17 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Description of the building or part you are proposing to demolish</t>
+          <t>Volume of part to be demolished in cubic metres</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3512,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>part-built-date</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Part built date</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3448,44 +3528,36 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Reason for demolition</t>
+          <t>The approximate date the part to be removed was built, in YYYY-MM format.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Immunity from listing</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>immunity-from-listing</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>cert-of-immunity-sought</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Certificate of immunity sought</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3496,12 +3568,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Has a certificate of immunity been sought</t>
+          <t>Description of the building or part you are proposing to demolish</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3515,17 +3587,17 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
+          <t>Details of any demolition that needs to take place as part of the development proposal.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>application-result</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Application result</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3536,7 +3608,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Provide the result of the application for a certificate of immunity</t>
+          <t>Reason for demolition</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3546,34 +3618,34 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Listed building alterations</t>
+          <t>Immunity from listing</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>lb-alter</t>
+          <t>immunity-from-listing</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>proposal-alter-lb</t>
+          <t>cert-of-immunity-sought</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Proposal alter listed building</t>
+          <t>Certificate of immunity sought</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3584,12 +3656,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>True or False if proposal includes alterations to a listed building</t>
+          <t>Has a certificate of immunity been sought</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3603,17 +3675,17 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Details of any changes being made to a listed building as part of development works</t>
+          <t>Whether the applicant has obtained a Certificate of Immunity (COI) meaning the building in question cannot be listed</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>proposal-alter-lb-types</t>
+          <t>application-result</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Proposal alteration types[]</t>
+          <t>Application result</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3624,12 +3696,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Select from a list of listed building alteration types, select all that apply</t>
+          <t>Provide the result of the application for a certificate of immunity</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -3639,8 +3711,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Listed building alterations</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>lb-alter</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Details of any changes being made to a listed building as part of development works</t>
@@ -3648,36 +3728,28 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>document-reference</t>
+          <t>proposal-alter-lb</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Document reference[]</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal alter listed building</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>True or False if proposal includes alterations to a listed building</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3687,29 +3759,21 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>lb-grade</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>Details of any changes being made to a listed building as part of development works</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>listed-building-grade</t>
+          <t>proposal-alter-lb-types</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
+          <t>Proposal alteration types[]</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3720,7 +3784,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Select from a list of listed building alteration types, select all that apply</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3730,7 +3794,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3739,28 +3803,36 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
+          <t>Details of any changes being made to a listed building as part of development works</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>listed-building</t>
+          <t>document-reference</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>Document reference[]</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3770,13 +3842,21 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>lb-grade</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>The grade of any listed building affected by the proposed development.</t>
@@ -3784,12 +3864,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>provided-by</t>
+          <t>listed-building-grade</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3800,7 +3880,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3810,34 +3890,26 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>proposal-material-details</t>
+          <t>listed-building</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Proposal material details</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3848,17 +3920,17 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Whether the proposal involves material details that need to be provided</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3867,36 +3939,28 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>What materials are being used for the proposed development</t>
+          <t>The grade of any listed building affected by the proposed development.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>provided-by</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>building-element-type</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Building element type</t>
-        </is>
-      </c>
+          <t>Provided by</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3906,13 +3970,21 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n"/>
-      <c r="B70" s="2" t="n"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>What materials are being used for the proposed development</t>
@@ -3920,41 +3992,33 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>building-elements</t>
+          <t>proposal-material-details</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Building elements[]</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>existing-materials</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Existing materials</t>
-        </is>
-      </c>
+          <t>Proposal material details</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials currently used for this building element</t>
+          <t>Whether the proposal involves material details that need to be provided</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3978,12 +4042,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>proposed-materials</t>
+          <t>building-element-type</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Proposed materials</t>
+          <t>Building element type</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3992,17 +4056,17 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Description of the materials proposed for this building element as part of the development</t>
+          <t>The part of building the materials relate to, such as walls, roofs, windows, or doors</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4090,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>materials-not-known</t>
+          <t>existing-materials</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Materials not known</t>
+          <t>Existing materials</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4040,12 +4104,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Indicates the materials for this building element are not yet known</t>
+          <t>Description of the materials currently used for this building element</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4064,33 +4128,41 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>providing-additional-material-information</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Providing additional material information</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>Building elements[]</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>proposed-materials</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Proposed materials</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
+          <t>Description of the materials proposed for this building element as part of the development</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4104,22 +4176,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>supporting-documents</t>
+          <t>building-elements</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
+          <t>Building elements[]</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>materials-not-known</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Materials not known</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4128,44 +4200,36 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Indicates the materials for this building element are not yet known</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Ownership certificates and agricultural land declaration</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>ownership-certs</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>sole-owner</t>
+          <t>providing-additional-material-information</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Sole owner</t>
+          <t>Providing additional material information</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4176,7 +4240,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Is the applicant the sole owner of the land?</t>
+          <t>Is the applicant providing additional materials information on submitted plan(s)/drawing(s)/design and access statement?</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -4195,44 +4259,36 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
+          <t>What materials are being used for the proposed development</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>lbc-owners</t>
+          <t>supporting-documents</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4242,13 +4298,21 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Ownership certificates and agricultural land declaration</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ownership-certs</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
@@ -4256,44 +4320,28 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>lbc-owners</t>
+          <t>sole-owner</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Owners of listed building[]</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Sole owner</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Is the applicant the sole owner of the land?</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4332,19 +4380,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -4354,7 +4402,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4388,19 +4436,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -4444,19 +4492,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4466,7 +4514,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4490,31 +4538,47 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>notice-served-date</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Notice served date</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Date when notice was served</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4528,28 +4592,52 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>ownership-cert-option</t>
+          <t>lbc-owners</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Ownership certificate type</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>The type of ownership certificate based on ownership and tenancy status</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4568,23 +4656,47 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>steps-taken</t>
+          <t>lbc-owners</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Steps taken</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
+          <t>Owners of listed building[]</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Description of steps taken to identify unknown owners or tenants</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -4608,22 +4720,22 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>lbc-owners</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
+          <t>Owners of listed building[]</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>newspaper-name</t>
+          <t>notice-served-date</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Newspaper name</t>
+          <t>Notice served date</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4632,17 +4744,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Name of the newspaper where notice was published</t>
+          <t>Date when notice was served</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4656,41 +4768,33 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>newspaper-notices</t>
+          <t>ownership-cert-option</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Newspaper notices[]</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>publication-date</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Publication date</t>
-        </is>
-      </c>
+          <t>Ownership certificate type</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Date when the notice was published</t>
+          <t>The type of ownership certificate based on ownership and tenancy status</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4808,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>steps-taken</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Steps taken</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4720,7 +4824,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Description of steps taken to identify unknown owners or tenants</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -4730,7 +4834,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4744,28 +4848,36 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>newspaper-name</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Newspaper name</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr"/>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Name of the newspaper where notice was published</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -4784,23 +4896,31 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>newspaper-notices</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>Newspaper notices[]</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>publication-date</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Publication date</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Date when the notice was published</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -4815,29 +4935,21 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -4848,12 +4960,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4867,17 +4979,17 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -4888,17 +5000,17 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4907,17 +5019,17 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Who will be affected by the proposal and whether they have been notified, such as agricultural tenants</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -4928,23 +5040,31 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -4952,12 +5072,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -4968,17 +5088,17 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4992,12 +5112,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5008,7 +5128,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -5023,29 +5143,21 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Description of the proposal</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>proposal-details</t>
-        </is>
-      </c>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Proposal description</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
@@ -5056,7 +5168,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -5066,7 +5178,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5075,17 +5187,17 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>proposal-started</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Proposal started</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
@@ -5096,17 +5208,17 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been started</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5115,17 +5227,17 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>What development, works or change of use is proposed</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>proposal-started-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Proposal start date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -5136,12 +5248,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -5151,8 +5263,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="2" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Description of the proposal</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>proposal-details</t>
+        </is>
+      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>What development, works or change of use is proposed</t>
@@ -5160,12 +5280,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Proposal completed</t>
+          <t>Proposal description</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -5176,12 +5296,12 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Has any work on the proposal already been completed</t>
+          <t>A description of what is being proposed, including the development, works, or change of use</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -5200,12 +5320,12 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>proposal-completed-date</t>
+          <t>proposal-started</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Proposal completion date</t>
+          <t>Proposal started</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
@@ -5216,44 +5336,36 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
+          <t>Has any work on the proposal already been started</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Related applications</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>related-applications</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>has-related-applications</t>
+          <t>proposal-started-date</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Has related applications</t>
+          <t>Proposal start date</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -5264,17 +5376,17 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Are there any related applications, previous proposals or demolitions for the site</t>
+          <t>The date when work on the proposal started, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5283,41 +5395,33 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>proposal-completed</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Proposal completed</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>The reference for the related application</t>
+          <t>Has any work on the proposal already been completed</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -5331,52 +5435,52 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Details of any other development proposals made for the site</t>
+          <t>What development, works or change of use is proposed</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>proposal-completed-date</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>Proposal completion date</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>A description of the related application</t>
+          <t>The date when work on the proposal was completed, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
-      <c r="B102" s="2" t="n"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Related applications</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>related-applications</t>
+        </is>
+      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Details of any other development proposals made for the site</t>
@@ -5384,78 +5488,62 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>related-applications</t>
+          <t>has-related-applications</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Related applications[]</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>decision-date</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Decision date</t>
-        </is>
-      </c>
+          <t>Has related applications</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>The date when the decision was made, in YYYY-MM-DD format</t>
+          <t>Are there any related applications, previous proposals or demolitions for the site</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5464,17 +5552,17 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>The reference for the related application</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5483,27 +5571,27 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -5512,7 +5600,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A description of the related application</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -5522,7 +5610,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5531,27 +5619,27 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of any other development proposals made for the site</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>related-applications</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Related applications[]</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>decision-date</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Decision date</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5560,12 +5648,12 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The date when the decision was made, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -5575,8 +5663,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
-      <c r="B106" s="2" t="n"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -5594,12 +5690,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
@@ -5608,17 +5704,17 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5642,31 +5738,39 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5690,26 +5794,34 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -5738,26 +5850,34 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -5786,21 +5906,29 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -5834,12 +5962,12 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -5848,12 +5976,12 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -5863,50 +5991,50 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5915,38 +6043,46 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5955,33 +6091,41 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -5991,8 +6135,16 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
-      <c r="B115" s="2" t="n"/>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -6000,36 +6152,28 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -6048,36 +6192,28 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -6096,39 +6232,175 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -6136,46 +6408,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A103:A111"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B68:B74"/>
-    <mergeCell ref="A99:A102"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B103:B111"/>
-    <mergeCell ref="B75:B88"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B89:B93"/>
-    <mergeCell ref="B94:B98"/>
-    <mergeCell ref="A68:A74"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B115:B120"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="B53:B61"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B77:B91"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A106:A114"/>
+    <mergeCell ref="A53:A61"/>
+    <mergeCell ref="B97:B101"/>
+    <mergeCell ref="A92:A96"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A94:A98"/>
-    <mergeCell ref="A112:A117"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A75:A88"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B112:B117"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A51:A59"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B106:B114"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="B70:B76"/>
     <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A77:A91"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="A89:A93"/>
+    <mergeCell ref="A115:A120"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
